--- a/data/trans_orig/IP36BS1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP36BS1-Provincia-trans_orig.xlsx
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>81,26%</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,26%</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,78%</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>788</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>846</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6649,44 +6649,44 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>48,55%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7499,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -7607,12 +7607,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -8558,12 +8558,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8573,12 +8573,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,95%</t>
         </is>
       </c>
     </row>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9466,12 +9466,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9481,12 +9481,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -9579,12 +9579,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9594,12 +9594,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9629,12 +9629,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20514</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9727,12 +9727,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9742,12 +9742,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14187</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>24451</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9777,12 +9777,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10198,7 +10198,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11327,12 +11327,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11377,12 +11377,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,08%</t>
         </is>
       </c>
     </row>
@@ -11744,12 +11744,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11759,12 +11759,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11814,12 +11814,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11829,12 +11829,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,7%</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2779</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11927,12 +11927,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -13334,12 +13334,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13349,12 +13349,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13369,12 +13369,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13384,12 +13384,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13487,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -14425,12 +14425,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14440,12 +14440,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,73%</t>
         </is>
       </c>
     </row>
@@ -14995,7 +14995,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -16289,7 +16289,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -16354,12 +16354,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -16369,12 +16369,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>4621</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -16432,12 +16432,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -16447,12 +16447,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -16467,12 +16467,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -16482,12 +16482,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -16849,12 +16849,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -16864,12 +16864,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -16899,12 +16899,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -16934,12 +16934,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>47,7%</t>
         </is>
       </c>
     </row>
@@ -16962,12 +16962,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -16977,12 +16977,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>2728</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -17032,12 +17032,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -17047,12 +17047,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,32%</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -17130,7 +17130,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -17145,12 +17145,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -17160,12 +17160,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -17345,7 +17345,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -17418,12 +17418,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -17433,12 +17433,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -17453,12 +17453,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -17468,12 +17468,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -17488,12 +17488,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -17503,12 +17503,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>63,06%</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -17940,12 +17940,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -17955,12 +17955,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -18023,7 +18023,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -18101,7 +18101,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -18131,12 +18131,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -18146,12 +18146,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -18166,12 +18166,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -18181,12 +18181,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -18326,12 +18326,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -18341,12 +18341,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -18411,12 +18411,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -18439,12 +18439,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22190</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -18454,12 +18454,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -18474,12 +18474,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -18489,12 +18489,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -18509,12 +18509,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>41862</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -18524,12 +18524,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -18607,7 +18607,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -18642,7 +18642,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -18891,12 +18891,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>11870</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -18906,12 +18906,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>8978</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -19004,12 +19004,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -19019,12 +19019,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -19039,12 +19039,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -19054,12 +19054,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -19074,12 +19074,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -19089,12 +19089,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -19117,12 +19117,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -19132,12 +19132,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -19152,12 +19152,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>9666</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -19167,12 +19167,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -19187,12 +19187,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>16237</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -19202,12 +19202,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -19731,12 +19731,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -19746,12 +19746,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -19766,12 +19766,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -19781,12 +19781,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -20075,7 +20075,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -20414,7 +20414,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -20449,7 +20449,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -20717,12 +20717,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -20732,12 +20732,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -20752,12 +20752,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -20787,12 +20787,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -20802,12 +20802,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -21259,7 +21259,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -21287,7 +21287,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -21317,12 +21317,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -21332,12 +21332,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -21352,12 +21352,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -21367,12 +21367,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -21395,12 +21395,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -21410,12 +21410,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -21430,12 +21430,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -21445,12 +21445,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -21465,12 +21465,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -21480,12 +21480,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -21778,7 +21778,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -21813,7 +21813,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -22230,7 +22230,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -22245,7 +22245,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -22343,7 +22343,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -22393,7 +22393,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -22456,7 +22456,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -22471,7 +22471,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -22486,12 +22486,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -22501,12 +22501,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>77,51%</t>
         </is>
       </c>
     </row>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -22849,7 +22849,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -22912,7 +22912,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -22947,7 +22947,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -23266,7 +23266,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -23281,12 +23281,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -23296,12 +23296,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -23442,7 +23442,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -23477,7 +23477,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -23492,7 +23492,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -23507,12 +23507,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -23522,12 +23522,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -24533,7 +24533,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -24548,7 +24548,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>79,15%</t>
         </is>
       </c>
     </row>
@@ -25822,12 +25822,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -25837,12 +25837,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -25857,12 +25857,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>6598</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -25872,12 +25872,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -25892,12 +25892,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -25907,12 +25907,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -26088,7 +26088,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -26103,7 +26103,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -26123,7 +26123,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -26294,7 +26294,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -26364,7 +26364,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -26442,7 +26442,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -26500,12 +26500,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -26515,12 +26515,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -26535,12 +26535,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>10774</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -26550,12 +26550,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -26585,12 +26585,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>73,33%</t>
         </is>
       </c>
     </row>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -26750,7 +26750,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -26843,12 +26843,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -26858,12 +26858,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -26913,12 +26913,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -26928,12 +26928,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -27295,12 +27295,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -27310,12 +27310,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -27350,7 +27350,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -27365,12 +27365,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -27380,12 +27380,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -27526,7 +27526,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -27541,7 +27541,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -27596,7 +27596,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -27756,7 +27756,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -27771,7 +27771,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>6316</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -27836,12 +27836,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -27864,12 +27864,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -27899,12 +27899,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -27914,12 +27914,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>17683</t>
+          <t>17385</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -28017,7 +28017,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -28032,7 +28032,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -28052,7 +28052,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -28067,7 +28067,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -28130,7 +28130,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -28145,7 +28145,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -28165,7 +28165,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -28180,7 +28180,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -28243,7 +28243,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -28258,7 +28258,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -28278,7 +28278,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -28293,7 +28293,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -28321,7 +28321,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -28351,12 +28351,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>6883</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -28366,12 +28366,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -28386,12 +28386,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -28401,12 +28401,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -28429,12 +28429,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -28444,12 +28444,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -28464,12 +28464,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -28499,12 +28499,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>13698</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -28514,12 +28514,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -28542,12 +28542,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10666</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -28557,12 +28557,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -28577,12 +28577,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -28592,12 +28592,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -28612,12 +28612,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>31113</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -28627,12 +28627,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -30162,7 +30162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -30182,7 +30182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -30212,12 +30212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -30227,12 +30227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -30255,12 +30255,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -30270,12 +30270,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -30295,7 +30295,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -30325,12 +30325,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>14516</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -30340,12 +30340,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -30521,7 +30521,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -30536,7 +30536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -30556,7 +30556,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -30571,7 +30571,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -30594,12 +30594,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -30609,12 +30609,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -30634,7 +30634,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -30649,7 +30649,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -30664,12 +30664,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>10371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -30679,12 +30679,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>48,37%</t>
         </is>
       </c>
     </row>
@@ -30742,12 +30742,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -30757,12 +30757,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -30777,12 +30777,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -30792,12 +30792,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -30860,7 +30860,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -30910,7 +30910,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -31281,7 +31281,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -31351,7 +31351,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -31366,7 +31366,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -31577,7 +31577,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -31592,7 +31592,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -31620,7 +31620,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -31635,7 +31635,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -31650,12 +31650,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -31665,12 +31665,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -31685,12 +31685,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -31700,12 +31700,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -31728,12 +31728,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -31743,12 +31743,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -31763,12 +31763,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -31778,12 +31778,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -31798,12 +31798,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -31813,12 +31813,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,47%</t>
         </is>
       </c>
     </row>
@@ -31846,7 +31846,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -31861,7 +31861,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -31896,7 +31896,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -31916,7 +31916,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -31931,7 +31931,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -33727,7 +33727,7 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -33742,7 +33742,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -33958,7 +33958,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -33973,7 +33973,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -34379,7 +34379,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -34394,7 +34394,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -34620,7 +34620,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -34655,7 +34655,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -34713,12 +34713,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -34728,12 +34728,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -34748,12 +34748,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -34763,12 +34763,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -34866,7 +34866,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -34881,7 +34881,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -34959,7 +34959,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -34979,7 +34979,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -34994,7 +34994,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -35252,7 +35252,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -35267,7 +35267,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -35360,12 +35360,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>414</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -35400,7 +35400,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -35430,12 +35430,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -35445,12 +35445,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -35621,12 +35621,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>739</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -35636,12 +35636,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -35656,12 +35656,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -35671,12 +35671,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -35739,7 +35739,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3717</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -35789,7 +35789,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -35817,7 +35817,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -35832,7 +35832,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -35867,7 +35867,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -35882,12 +35882,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -35897,12 +35897,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>34,21%</t>
         </is>
       </c>
     </row>
@@ -35925,12 +35925,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -35940,12 +35940,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -35965,7 +35965,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -35980,7 +35980,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -35995,12 +35995,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -36010,12 +36010,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -36268,12 +36268,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -36283,12 +36283,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -36308,7 +36308,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -36323,7 +36323,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -36338,12 +36338,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -36353,12 +36353,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -36381,12 +36381,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>396</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -36396,12 +36396,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -36416,12 +36416,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -36431,12 +36431,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -36451,12 +36451,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -36466,12 +36466,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,49%</t>
         </is>
       </c>
     </row>
@@ -36720,12 +36720,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>929</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>6370</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -36735,12 +36735,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -36755,12 +36755,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -36770,12 +36770,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -36790,12 +36790,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -36805,12 +36805,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -36833,12 +36833,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>469</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -36848,12 +36848,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -36873,7 +36873,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -36888,7 +36888,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -36903,12 +36903,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -36918,12 +36918,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -36986,7 +36986,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -37001,7 +37001,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -37036,7 +37036,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -37289,12 +37289,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -37304,12 +37304,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -37324,12 +37324,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>394</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -37339,12 +37339,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -37359,12 +37359,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>12015</t>
+          <t>11199</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -37374,12 +37374,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -37402,12 +37402,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -37417,12 +37417,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -37437,12 +37437,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -37452,12 +37452,12 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -37472,12 +37472,12 @@
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>35003</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -37487,12 +37487,12 @@
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,18%</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -37648,7 +37648,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -37663,12 +37663,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -37678,12 +37678,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -37698,12 +37698,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -37713,12 +37713,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -37741,12 +37741,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -37756,12 +37756,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -37776,12 +37776,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -37791,12 +37791,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -37811,12 +37811,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>14609</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>28937</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -37826,12 +37826,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -37854,12 +37854,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -37869,12 +37869,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -37889,12 +37889,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6095</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -37904,12 +37904,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -37939,12 +37939,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -37967,12 +37967,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -37982,12 +37982,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -38002,12 +38002,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -38017,12 +38017,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -38037,12 +38037,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>18263</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -38052,12 +38052,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
